--- a/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92554158915</v>
+        <v>46157.93109441126</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93109441126</v>
+        <v>46157.93133664006</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93133664006</v>
+        <v>46157.93381440581</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93381440581</v>
+        <v>46157.93692887857</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93692887857</v>
+        <v>46158.28203860502</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28203860502</v>
+        <v>46158.29650524812</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29650524812</v>
+        <v>46158.29805227451</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29805227451</v>
+        <v>46158.33368391382</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33368391382</v>
+        <v>46158.37220281234</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/17. ООО Клиентская база/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37220281234</v>
+        <v>46158.37274437217</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
